--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104552_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104552_W11.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2656</v>
+        <v>4.8776</v>
       </c>
       <c r="E2" t="n">
-        <v>2.526</v>
+        <v>1.9711</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7396</v>
+        <v>2.9065</v>
       </c>
       <c r="G2" t="n">
-        <v>3.437</v>
+        <v>3.4397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9927</v>
+        <v>0.9937</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4443</v>
+        <v>2.446</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4786</v>
+        <v>3.4466</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3494</v>
+        <v>0.334</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0416</v>
+        <v>-0.0069</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6849</v>
+        <v>-0.6665</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2129</v>
+        <v>-0.6108</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1815</v>
+        <v>-0.3373</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3944</v>
+        <v>-0.2734</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0394</v>
+        <v>2.524</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1193</v>
+        <v>1.2829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9201</v>
+        <v>1.241</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0169</v>
+        <v>-0.6129</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5686</v>
+        <v>-0.0144</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5516</v>
+        <v>-0.5984</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9594</v>
+        <v>0.6446</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8848</v>
+        <v>-0.1002</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.7447</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9425</v>
+        <v>-1.2574</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3162</v>
+        <v>0.0857</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6263</v>
+        <v>-1.3432</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.7635</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4661</v>
+        <v>0.9304</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9629</v>
+        <v>0.4806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5032</v>
+        <v>0.4498</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5978</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9604</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8233</v>
+        <v>1.7585</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3264</v>
+        <v>0.9186</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4969</v>
+        <v>0.8398</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6236</v>
+        <v>2.0267</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0159</v>
+        <v>2.5622</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6077</v>
+        <v>-0.5355</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6526</v>
+        <v>2.939</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.09370000000000001</v>
+        <v>2.8646</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7463</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2762</v>
+        <v>-0.9124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.3023</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.354</v>
+        <v>-0.61</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.7803</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2447</v>
+        <v>1.1869</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4869</v>
+        <v>0.8101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7316</v>
+        <v>0.3768</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.5936</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>1.9497</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6589</v>
+        <v>0.8288</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4864</v>
+        <v>-0.5016</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8275</v>
+        <v>1.3304</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0101</v>
+        <v>0.8817</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6235</v>
+        <v>0.1267</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3866</v>
+        <v>0.755</v>
       </c>
       <c r="J5" t="n">
-        <v>1.884</v>
+        <v>-0.0822</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7348</v>
+        <v>-0.0592</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1493</v>
+        <v>-0.023</v>
       </c>
       <c r="M5" t="n">
-        <v>0.126</v>
+        <v>0.9639</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1113</v>
+        <v>0.1859</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2373</v>
+        <v>0.778</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-4.7803</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6504</v>
+        <v>0.2429</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8026</v>
+        <v>0.3899</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1521</v>
+        <v>-0.1471</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4553</v>
+        <v>1.5253</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>3.9709</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.616</v>
+        <v>-2.4457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0989</v>
+        <v>0.1518</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3923</v>
+        <v>1.1623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4912</v>
+        <v>-1.0104</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4825</v>
+        <v>2.0086</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4184</v>
+        <v>1.6119</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9009</v>
+        <v>0.3967</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4135</v>
+        <v>1.8619</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3361</v>
+        <v>1.713</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1467</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7546</v>
+        <v>-0.1011</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8236</v>
+        <v>0.2477</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5399</v>
+        <v>0.1337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0212</v>
+        <v>0.5084</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5187</v>
+        <v>-0.3747</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-2.4457</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-2.6034</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.389</v>
+        <v>0.114</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5208</v>
+        <v>2.8565</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1318</v>
+        <v>-2.7424</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8925</v>
+        <v>0.0027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1329</v>
+        <v>1.7759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7596000000000001</v>
+        <v>-1.7731</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0467</v>
+        <v>2.5493</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0386</v>
+        <v>2.5953</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0081</v>
+        <v>-0.046</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9392</v>
+        <v>-2.5466</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1715</v>
+        <v>-0.8194</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7678</v>
+        <v>-1.7271</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8147</v>
+        <v>2.7316</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7635</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9966</v>
+        <v>-0.4901</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>-0.1677</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3009</v>
+        <v>-0.3224</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5297</v>
+        <v>-2.1301</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9851</v>
+        <v>0.7025</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4553</v>
+        <v>-2.8326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1203</v>
+        <v>-0.2795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2541</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3744</v>
+        <v>0.3581</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3156</v>
+        <v>-0.4757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0389</v>
+        <v>0.4193</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3545</v>
+        <v>-0.895</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9497</v>
+        <v>-0.4236</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1661</v>
+        <v>-0.3415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7837</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2653</v>
+        <v>-0.0521</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1272</v>
+        <v>0.7608</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1381</v>
+        <v>-0.8129</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0731</v>
+        <v>0.1476</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6956</v>
+        <v>-0.214</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3775</v>
+        <v>0.3616</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3909</v>
+        <v>-0.8126</v>
       </c>
       <c r="E9" t="n">
-        <v>1.84</v>
+        <v>0.5987</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2309</v>
+        <v>-1.4112</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0304</v>
+        <v>-0.3039</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7924</v>
+        <v>0.0429</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.762</v>
+        <v>-0.3467</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6119</v>
+        <v>0.9404</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6281</v>
+        <v>0.1584</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0162</v>
+        <v>0.782</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5815</v>
+        <v>-1.2442</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8357</v>
+        <v>-0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7458</v>
+        <v>-1.1287</v>
       </c>
       <c r="P9" t="n">
-        <v>2.722</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9488</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0094</v>
+        <v>-0.785</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2521</v>
+        <v>-0.3417</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7573</v>
+        <v>-0.4433</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1339</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8409</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3679</v>
+        <v>-4.8266</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.28</v>
+        <v>-1.8981</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0878</v>
+        <v>-2.9285</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2127</v>
+        <v>-3.2298</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2695</v>
+        <v>-1.2858</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9432</v>
+        <v>-1.944</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0843</v>
+        <v>-0.1209</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3401</v>
+        <v>-0.3662</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1284</v>
+        <v>-3.1089</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2462</v>
+        <v>0.3042</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>0.7268</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5456</v>
+        <v>-0.4226</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.909</v>
+        <v>-1.9009</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.909</v>
+        <v>-1.9009</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8958</v>
+        <v>-6.9225</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5435</v>
+        <v>-5.5936</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3523</v>
+        <v>-1.329</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7713</v>
+        <v>-2.7765</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8681</v>
+        <v>-2.8659</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1306</v>
+        <v>-0.1558</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6958</v>
+        <v>0.6787</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6407</v>
+        <v>-2.6207</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.3017</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7531</v>
+        <v>-0.757</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.277800000000003</v>
+        <v>-2.586499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1844000000000001</v>
+        <v>0.1592000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0933</v>
+        <v>-2.745699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9811999999999994</v>
+        <v>0.9606000000000008</v>
       </c>
       <c r="H12" t="n">
-        <v>6.3788</v>
+        <v>6.321800000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.3975</v>
+        <v>-5.3609</v>
       </c>
       <c r="J12" t="n">
-        <v>11.8611</v>
+        <v>11.5993</v>
       </c>
       <c r="K12" t="n">
-        <v>7.6505</v>
+        <v>7.476900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.210900000000001</v>
+        <v>4.1224</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.88</v>
+        <v>-10.6386</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2716</v>
+        <v>-1.1551</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.6083</v>
+        <v>-9.4834</v>
       </c>
       <c r="P12" t="n">
-        <v>1.134200000000001</v>
+        <v>1.138199999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.5492</v>
+        <v>-21.625</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6834</v>
+        <v>22.7632</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09079999999999977</v>
+        <v>0.6045</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4368</v>
+        <v>2.1568</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5274</v>
+        <v>-1.5523</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.3027</v>
+        <v>-5.289499999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>8.066700000000001</v>
+        <v>8.0282</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.3693</v>
+        <v>-13.3178</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9099</v>
+        <v>4.9886</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2503</v>
+        <v>4.4968</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6597</v>
+        <v>0.4918</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3266</v>
+        <v>-0.3189</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4243</v>
+        <v>-2.4132</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0977</v>
+        <v>2.0942</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2062</v>
+        <v>2.1736</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1469</v>
+        <v>-1.1623</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3531</v>
+        <v>3.336</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5328</v>
+        <v>-2.4925</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2774</v>
+        <v>-1.2508</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5295</v>
+        <v>0.605</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1251</v>
+        <v>0.4221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4043</v>
+        <v>0.1829</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3441</v>
+        <v>4.6313</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7169</v>
+        <v>2.089</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6271</v>
+        <v>2.5423</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5397</v>
+        <v>0.5399</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7489</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9036</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2252</v>
+        <v>-0.1993</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4348</v>
+        <v>0.7224</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7561</v>
+        <v>0.1691</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6787</v>
+        <v>0.5532</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.874</v>
+        <v>3.2159</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2872</v>
+        <v>2.0785</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5869</v>
+        <v>1.1375</v>
       </c>
       <c r="G15" t="n">
-        <v>0.785</v>
+        <v>5.3179</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6118</v>
+        <v>0.2613</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1733</v>
+        <v>5.0565</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9232</v>
+        <v>5.5317</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8485</v>
+        <v>0.9373</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>4.5944</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1381</v>
+        <v>-0.2138</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2368</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1817</v>
+        <v>-0.993</v>
       </c>
       <c r="T15" t="n">
-        <v>1.364</v>
+        <v>-0.3558</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1824</v>
+        <v>-0.6372</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1897</v>
+        <v>2.1526</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3092</v>
+        <v>1.4601</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8806</v>
+        <v>0.6925</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3335</v>
+        <v>0.7904</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2612</v>
+        <v>0.6145</v>
       </c>
       <c r="I16" t="n">
-        <v>5.0724</v>
+        <v>0.1759</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5747</v>
+        <v>0.9191</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9555</v>
+        <v>0.8446</v>
       </c>
       <c r="L16" t="n">
-        <v>4.6192</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2411</v>
+        <v>-0.1287</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6944</v>
+        <v>-0.2301</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4532</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1757</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0345</v>
+        <v>0.4517</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1825</v>
+        <v>0.5411</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.852</v>
+        <v>-0.0893</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6556</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1762,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1525</v>
+        <v>0.0764</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4227</v>
+        <v>-0.237</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2701</v>
+        <v>0.3134</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4912</v>
+        <v>1.4923</v>
       </c>
       <c r="H18" t="n">
         <v>0.6089</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8823</v>
+        <v>0.8834</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0496</v>
+        <v>2.0191</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9728</v>
+        <v>0.9545</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0768</v>
+        <v>1.0645</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5584</v>
+        <v>-0.5268</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4023</v>
+        <v>-0.1672</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2571</v>
+        <v>-0.019</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1452</v>
+        <v>-0.1482</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3342</v>
+        <v>-0.3382</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7483</v>
+        <v>-1.7432</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.443</v>
+        <v>-0.3251</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0149</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4281</v>
+        <v>-1.2077</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4248</v>
+        <v>-0.8331</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1876</v>
+        <v>0.6858</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2372</v>
+        <v>-1.5188</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0546</v>
+        <v>0.2673</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>-0.6495</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4795</v>
+        <v>-1.1004</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.205</v>
+        <v>-0.231</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2745</v>
+        <v>-0.8694</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6986</v>
+        <v>-0.5911</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0696</v>
+        <v>-0.1979</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6291</v>
+        <v>-0.3932</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2667</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.4457</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7085</v>
+        <v>-0.4362</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6693</v>
+        <v>-0.0152</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0392</v>
+        <v>-0.421</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3361</v>
+        <v>-0.4177</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1358</v>
+        <v>-0.184</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7997</v>
+        <v>-0.2337</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6009</v>
+        <v>0.0545</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1559</v>
+        <v>0.0172</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4451</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9371</v>
+        <v>-0.4722</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2917</v>
+        <v>-0.2012</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>-0.271</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2365</v>
+        <v>-0.7014</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0907</v>
+        <v>-0.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3273</v>
+        <v>-0.6317</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8163</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3047</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1111</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4158</v>
+        <v>0.0523</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8245</v>
+        <v>-0.3237</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6737</v>
+        <v>-1.1236</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4982</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.312</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.928</v>
+        <v>0.1551</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.616</v>
+        <v>0.4392</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1365</v>
+        <v>-0.918</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2543</v>
+        <v>-1.2788</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8822</v>
+        <v>0.3608</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5712</v>
+        <v>-0.1743</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0253</v>
+        <v>0.0926</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.2669</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.27</v>
+        <v>-0.8114</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4553</v>
+        <v>-0.8114</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9315</v>
+        <v>-1.6868</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5367</v>
+        <v>-0.9759</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3948</v>
+        <v>-0.7109</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1108</v>
+        <v>1.1202</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2899</v>
+        <v>0.301</v>
       </c>
       <c r="I22" t="n">
-        <v>0.821</v>
+        <v>0.8192</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3992</v>
+        <v>3.3842</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L22" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2884</v>
+        <v>-2.264</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3602</v>
+        <v>0.6075</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>0.1925</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7594</v>
+        <v>0.4149</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8411</v>
+        <v>-3.0949</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1246</v>
+        <v>-1.4927</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7165</v>
+        <v>-1.6021</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1301</v>
+        <v>-3.1286</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8556</v>
+        <v>-2.8576</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0067</v>
+        <v>-1.0209</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.753</v>
+        <v>-1.7656</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1234</v>
+        <v>-2.1077</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9034</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0162</v>
+        <v>0.6663</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1128</v>
+        <v>-0.0196</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8159</v>
+        <v>-5.7698</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.813</v>
+        <v>-4.8616</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0029</v>
+        <v>-0.9082</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.3407</v>
+        <v>-5.3393</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7605</v>
+        <v>-2.7546</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5803</v>
+        <v>-2.5847</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.9828</v>
+        <v>-4.0056</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7357</v>
+        <v>-1.7484</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3579</v>
+        <v>-1.3337</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3756</v>
+        <v>-0.3137</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1089</v>
+        <v>0.1111</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4845</v>
+        <v>-0.4248</v>
       </c>
       <c r="V24" t="n">
-        <v>2.6224</v>
+        <v>2.6147</v>
       </c>
       <c r="W24" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.277800000000002</v>
+        <v>3.283400000000004</v>
       </c>
       <c r="E25" t="n">
-        <v>3.093500000000002</v>
+        <v>2.745700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1843999999999997</v>
+        <v>0.5378000000000002</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9812999999999992</v>
+        <v>-0.9605999999999995</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.3786</v>
+        <v>-6.3216</v>
       </c>
       <c r="I25" t="n">
-        <v>5.397500000000003</v>
+        <v>5.360799999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>10.8798</v>
+        <v>10.6386</v>
       </c>
       <c r="K25" t="n">
-        <v>1.271599999999999</v>
+        <v>1.1552</v>
       </c>
       <c r="L25" t="n">
-        <v>9.608200000000002</v>
+        <v>9.4833</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.8611</v>
+        <v>-11.5992</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.6505</v>
+        <v>-7.476799999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.2108</v>
+        <v>-4.1224</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-22.6834</v>
+        <v>-22.7633</v>
       </c>
       <c r="R25" t="n">
-        <v>21.5492</v>
+        <v>21.625</v>
       </c>
       <c r="S25" t="n">
-        <v>0.09090000000000031</v>
+        <v>0.09260000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5273</v>
+        <v>1.5524</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4368</v>
+        <v>-1.459900000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3026</v>
+        <v>5.2895</v>
       </c>
       <c r="W25" t="n">
-        <v>13.3692</v>
+        <v>13.3177</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.0665</v>
+        <v>-8.0282</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104552_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104552_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.4457</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.6034</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.8326</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.9009</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-13.3178</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.7432</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.4457</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.8114</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104552_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
